--- a/5. Knife/output/yearly_surface_area_growth_param_0.5.xlsx
+++ b/5. Knife/output/yearly_surface_area_growth_param_0.5.xlsx
@@ -775,13 +775,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>83.66159411280043</v>
+        <v>83.08727170581606</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2307107104980004</v>
+        <v>0.45553093477052</v>
       </c>
       <c r="D2" t="n">
-        <v>32.33484238707295</v>
+        <v>62.67182819600364</v>
       </c>
     </row>
     <row r="3">
@@ -789,13 +789,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>239.6887932533375</v>
+        <v>237.2491502082842</v>
       </c>
       <c r="C3" t="n">
-        <v>1.492256510455152</v>
+        <v>2.528000338435537</v>
       </c>
       <c r="D3" t="n">
-        <v>62.48333263678825</v>
+        <v>106.7257929286708</v>
       </c>
     </row>
     <row r="4">
@@ -803,13 +803,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>358.211266596238</v>
+        <v>354.66323039309</v>
       </c>
       <c r="C4" t="n">
-        <v>6.151631114810514</v>
+        <v>9.240209392370978</v>
       </c>
       <c r="D4" t="n">
-        <v>63.59663453340413</v>
+        <v>85.3698351181899</v>
       </c>
     </row>
     <row r="5">
@@ -817,13 +817,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>400.013102095363</v>
+        <v>406.8362486398783</v>
       </c>
       <c r="C5" t="n">
-        <v>12.37002107350981</v>
+        <v>17.35239067256238</v>
       </c>
       <c r="D5" t="n">
-        <v>44.00684084286328</v>
+        <v>55.95961914206821</v>
       </c>
     </row>
     <row r="6">
@@ -831,13 +831,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>380.8611678809162</v>
+        <v>394.7882408133614</v>
       </c>
       <c r="C6" t="n">
-        <v>14.00757624419349</v>
+        <v>19.48180144307371</v>
       </c>
       <c r="D6" t="n">
-        <v>32.12082138754715</v>
+        <v>36.46800022195202</v>
       </c>
     </row>
     <row r="7">
@@ -845,13 +845,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>365.3682073601972</v>
+        <v>373.8721059743831</v>
       </c>
       <c r="C7" t="n">
-        <v>10.18072369303942</v>
+        <v>13.89369351050086</v>
       </c>
       <c r="D7" t="n">
-        <v>28.38625312059227</v>
+        <v>29.22466566001905</v>
       </c>
     </row>
     <row r="8">
@@ -859,13 +859,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>380.9426529403686</v>
+        <v>403.4737627528329</v>
       </c>
       <c r="C8" t="n">
-        <v>5.841398840268521</v>
+        <v>7.510369937488099</v>
       </c>
       <c r="D8" t="n">
-        <v>33.21252483466959</v>
+        <v>30.54217107911827</v>
       </c>
     </row>
     <row r="9">
@@ -873,13 +873,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>241.0671670301</v>
+        <v>299.5312245657018</v>
       </c>
       <c r="C9" t="n">
-        <v>4.326562132615692</v>
+        <v>4.548437113775471</v>
       </c>
       <c r="D9" t="n">
-        <v>38.05155926890212</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -887,13 +887,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>66.90610604442013</v>
+        <v>97.51209072431445</v>
       </c>
       <c r="C10" t="n">
-        <v>4.128249096357838</v>
+        <v>3.843542262126263</v>
       </c>
       <c r="D10" t="n">
-        <v>37.29659528433633</v>
+        <v>36.58482819875739</v>
       </c>
     </row>
     <row r="11">
@@ -901,13 +901,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>25.41057582902019</v>
+        <v>23.45591614986479</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.553926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>38.56010457970196</v>
+        <v>39.98167525545134</v>
       </c>
     </row>
     <row r="12">
@@ -918,10 +918,10 @@
         <v>23.86628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="D12" t="n">
-        <v>37.96909246174538</v>
+        <v>41.22358610132357</v>
       </c>
     </row>
     <row r="13">
@@ -929,13 +929,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20.29272504678157</v>
+        <v>22.11386703815941</v>
       </c>
       <c r="C13" t="n">
-        <v>3.121957699504857</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="D13" t="n">
-        <v>37.20332925243289</v>
+        <v>41.62610266006477</v>
       </c>
     </row>
     <row r="14">
@@ -943,13 +943,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16.59349969717959</v>
+        <v>19.97365704290136</v>
       </c>
       <c r="C14" t="n">
         <v>3.380157345721768</v>
       </c>
       <c r="D14" t="n">
-        <v>34.10886048864694</v>
+        <v>40.56188814866123</v>
       </c>
     </row>
     <row r="15">
@@ -957,13 +957,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14.69185439405351</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>29.02537087605695</v>
+        <v>39.77550823755952</v>
       </c>
     </row>
     <row r="16">
@@ -971,13 +971,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14.05273663858884</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
-        <v>20.66578917439536</v>
+        <v>38.43836786437537</v>
       </c>
     </row>
     <row r="17">
@@ -985,13 +985,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>11.33329549782518</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="C17" t="n">
-        <v>4.249985811684442</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="D17" t="n">
-        <v>11.8055161435679</v>
+        <v>34.47210713921825</v>
       </c>
     </row>
     <row r="18">
@@ -999,13 +999,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>6.42062998577414</v>
+        <v>11.77115497391926</v>
       </c>
       <c r="C18" t="n">
-        <v>3.21031499288707</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="D18" t="n">
-        <v>3.745367491701582</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -1013,13 +1013,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>1.805434028109884</v>
+        <v>10.83260416865931</v>
       </c>
       <c r="C19" t="n">
-        <v>1.203622685406589</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>22.8688310227252</v>
       </c>
     </row>
     <row r="20">
@@ -1027,13 +1027,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>10.75995483854504</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -1041,13 +1041,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>40.77073057654017</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>11.77821105544494</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.718048705102678</v>
       </c>
     </row>
   </sheetData>
@@ -1086,13 +1086,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>95.05772146369742</v>
+        <v>91.1376028806399</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2061670178918302</v>
+        <v>0.4250967559388689</v>
       </c>
       <c r="D2" t="n">
-        <v>26.68782959224529</v>
+        <v>51.99335841691108</v>
       </c>
     </row>
     <row r="3">
@@ -1100,13 +1100,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>276.6859554878786</v>
+        <v>265.935818126376</v>
       </c>
       <c r="C3" t="n">
-        <v>1.315541923690726</v>
+        <v>2.287472150895068</v>
       </c>
       <c r="D3" t="n">
-        <v>65.43839322657115</v>
+        <v>112.8322636490859</v>
       </c>
     </row>
     <row r="4">
@@ -1114,13 +1114,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>433.9962988778663</v>
+        <v>417.6727797993545</v>
       </c>
       <c r="C4" t="n">
-        <v>5.48796966673967</v>
+        <v>8.35958170166159</v>
       </c>
       <c r="D4" t="n">
-        <v>67.34887425903544</v>
+        <v>94.86529891366503</v>
       </c>
     </row>
     <row r="5">
@@ -1128,13 +1128,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>493.0336970727483</v>
+        <v>479.8537341432348</v>
       </c>
       <c r="C5" t="n">
-        <v>11.97732199181109</v>
+        <v>16.91060420565131</v>
       </c>
       <c r="D5" t="n">
-        <v>46.41212271826797</v>
+        <v>61.50649367106269</v>
       </c>
     </row>
     <row r="6">
@@ -1142,13 +1142,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>482.9393671776826</v>
+        <v>485.3142148742556</v>
       </c>
       <c r="C6" t="n">
-        <v>15.13462260866883</v>
+        <v>20.97111271041612</v>
       </c>
       <c r="D6" t="n">
-        <v>33.61013265488955</v>
+        <v>38.84284791852506</v>
       </c>
     </row>
     <row r="7">
@@ -1156,13 +1156,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>432.5609837342574</v>
+        <v>437.1722527011046</v>
       </c>
       <c r="C7" t="n">
-        <v>12.0970952117292</v>
+        <v>16.70836417857646</v>
       </c>
       <c r="D7" t="n">
-        <v>29.16477905005999</v>
+        <v>30.06307819944583</v>
       </c>
     </row>
     <row r="8">
@@ -1170,13 +1170,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>409.8158529222673</v>
+        <v>420.9979592736385</v>
       </c>
       <c r="C8" t="n">
-        <v>7.093127163183205</v>
+        <v>9.596583809012571</v>
       </c>
       <c r="D8" t="n">
-        <v>32.96217917008666</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="9">
@@ -1184,13 +1184,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>314.7296607751466</v>
+        <v>369.7546561027718</v>
       </c>
       <c r="C9" t="n">
-        <v>4.77031209493525</v>
+        <v>5.324999547834698</v>
       </c>
       <c r="D9" t="n">
-        <v>37.49687181600267</v>
+        <v>33.50312215512664</v>
       </c>
     </row>
     <row r="10">
@@ -1198,13 +1198,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>127.5486617357456</v>
+        <v>192.6041733576605</v>
       </c>
       <c r="C10" t="n">
-        <v>4.270602513473626</v>
+        <v>4.128249096357838</v>
       </c>
       <c r="D10" t="n">
-        <v>37.01188845010476</v>
+        <v>36.15776794741003</v>
       </c>
     </row>
     <row r="11">
@@ -1212,13 +1212,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>37.13853390395258</v>
+        <v>54.73047101635117</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.553926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>38.02701557629594</v>
+        <v>39.44858625204532</v>
       </c>
     </row>
     <row r="12">
@@ -1226,13 +1226,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>24.30021917551705</v>
+        <v>23.86628669023996</v>
       </c>
       <c r="C12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="D12" t="n">
-        <v>37.10122749119121</v>
+        <v>40.57268737340794</v>
       </c>
     </row>
     <row r="13">
@@ -1240,13 +1240,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20.55288818840698</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="C13" t="n">
-        <v>3.121957699504857</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="D13" t="n">
-        <v>35.90251354430586</v>
+        <v>41.36593951843936</v>
       </c>
     </row>
     <row r="14">
@@ -1254,13 +1254,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>16.90078672860884</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="C14" t="n">
         <v>3.380157345721768</v>
       </c>
       <c r="D14" t="n">
-        <v>32.57242533150067</v>
+        <v>39.94731408580272</v>
       </c>
     </row>
     <row r="15">
@@ -1268,13 +1268,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.97517856995334</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>26.51700549170635</v>
+        <v>39.05883241345935</v>
       </c>
     </row>
     <row r="16">
@@ -1282,13 +1282,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>12.81278928812512</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>4.133157834879071</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
-        <v>17.77257868998001</v>
+        <v>38.02505208088746</v>
       </c>
     </row>
     <row r="17">
@@ -1296,13 +1296,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>9.444412914854317</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="C17" t="n">
         <v>3.777765165941727</v>
       </c>
       <c r="D17" t="n">
-        <v>8.9721922691116</v>
+        <v>33.99988649347554</v>
       </c>
     </row>
     <row r="18">
@@ -1310,13 +1310,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>4.280419990516093</v>
+        <v>11.77115497391926</v>
       </c>
       <c r="C18" t="n">
-        <v>2.140209995258047</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="D18" t="n">
-        <v>2.140209995258047</v>
+        <v>28.35778243716912</v>
       </c>
     </row>
     <row r="19">
@@ -1324,13 +1324,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6018113427032947</v>
+        <v>10.23079282595601</v>
       </c>
       <c r="C19" t="n">
-        <v>0.6018113427032947</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>22.26701968002191</v>
       </c>
     </row>
     <row r="20">
@@ -1338,13 +1338,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>10.08745766113597</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>15.46743508040849</v>
       </c>
     </row>
     <row r="21">
@@ -1352,13 +1352,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>40.33504049664705</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>11.91717105582754</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.750116397498662</v>
       </c>
     </row>
   </sheetData>
@@ -1397,13 +1397,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>101.0925246017026</v>
+        <v>94.11426191991623</v>
       </c>
       <c r="C2" t="n">
-        <v>0.150207398749762</v>
+        <v>0.3239767424014474</v>
       </c>
       <c r="D2" t="n">
-        <v>30.69041498245954</v>
+        <v>61.02249205286899</v>
       </c>
     </row>
     <row r="3">
@@ -1411,13 +1411,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>306.0058506752096</v>
+        <v>284.5252109062894</v>
       </c>
       <c r="C3" t="n">
-        <v>1.178097245096172</v>
+        <v>2.100940087088174</v>
       </c>
       <c r="D3" t="n">
-        <v>65.45311944213485</v>
+        <v>114.2950677284137</v>
       </c>
     </row>
     <row r="4">
@@ -1425,13 +1425,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>492.7048115918255</v>
+        <v>460.9256384053562</v>
       </c>
       <c r="C4" t="n">
-        <v>4.951935420220911</v>
+        <v>7.58105577219387</v>
       </c>
       <c r="D4" t="n">
-        <v>71.86687719397926</v>
+        <v>102.4974055664797</v>
       </c>
     </row>
     <row r="5">
@@ -1439,13 +1439,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>583.6490101747289</v>
+        <v>544.1827524640071</v>
       </c>
       <c r="C5" t="n">
-        <v>11.46190444708151</v>
+        <v>16.22338081267855</v>
       </c>
       <c r="D5" t="n">
-        <v>48.17926858591223</v>
+        <v>65.99798941799185</v>
       </c>
     </row>
     <row r="6">
@@ -1453,13 +1453,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>581.3949174457782</v>
+        <v>566.0992882136129</v>
       </c>
       <c r="C6" t="n">
-        <v>15.77864910265474</v>
+        <v>21.81639748377262</v>
       </c>
       <c r="D6" t="n">
-        <v>34.97868895460962</v>
+        <v>41.94222542083224</v>
       </c>
     </row>
     <row r="7">
@@ -1467,13 +1467,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>508.1378855025853</v>
+        <v>509.3955043117255</v>
       </c>
       <c r="C7" t="n">
-        <v>13.71403368062369</v>
+        <v>18.74450891718435</v>
       </c>
       <c r="D7" t="n">
-        <v>29.46421209985527</v>
+        <v>30.78171751895449</v>
       </c>
     </row>
     <row r="8">
@@ -1481,13 +1481,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>449.0366737069273</v>
+        <v>453.7097927791422</v>
       </c>
       <c r="C8" t="n">
-        <v>8.17795837637593</v>
+        <v>11.76624623539802</v>
       </c>
       <c r="D8" t="n">
-        <v>32.71183350550372</v>
+        <v>30.37527396939631</v>
       </c>
     </row>
     <row r="9">
@@ -1495,13 +1495,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>362.6546567056589</v>
+        <v>408.1390278434136</v>
       </c>
       <c r="C9" t="n">
-        <v>5.214062057254808</v>
+        <v>6.434374453633594</v>
       </c>
       <c r="D9" t="n">
-        <v>36.83124687252333</v>
+        <v>33.17030968338697</v>
       </c>
     </row>
     <row r="10">
@@ -1509,13 +1509,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>179.7923658172396</v>
+        <v>263.0691148299753</v>
       </c>
       <c r="C10" t="n">
         <v>4.412955930589413</v>
       </c>
       <c r="D10" t="n">
-        <v>36.58482819875739</v>
+        <v>36.01541453029424</v>
       </c>
     </row>
     <row r="11">
@@ -1523,13 +1523,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>55.08586368528852</v>
+        <v>104.6631410020482</v>
       </c>
       <c r="C11" t="n">
-        <v>4.264712027248144</v>
+        <v>3.553926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>36.96083756948391</v>
+        <v>38.73780091417063</v>
       </c>
     </row>
     <row r="12">
@@ -1537,13 +1537,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>26.03594911662541</v>
+        <v>33.62976760897449</v>
       </c>
       <c r="C12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="D12" t="n">
-        <v>36.23336252063703</v>
+        <v>39.92178864549229</v>
       </c>
     </row>
     <row r="13">
@@ -1551,13 +1551,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>21.07321447165778</v>
+        <v>22.63419332141022</v>
       </c>
       <c r="C13" t="n">
-        <v>3.121957699504857</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="D13" t="n">
-        <v>34.86186097780424</v>
+        <v>40.58545009356315</v>
       </c>
     </row>
     <row r="14">
@@ -1565,13 +1565,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15.97892563432109</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="C14" t="n">
         <v>3.380157345721768</v>
       </c>
       <c r="D14" t="n">
-        <v>30.72870314292517</v>
+        <v>39.64002705437346</v>
       </c>
     </row>
     <row r="15">
@@ -1579,13 +1579,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.25850274585317</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>24.00864010735575</v>
+        <v>38.34215658935918</v>
       </c>
     </row>
     <row r="16">
@@ -1593,13 +1593,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11.5728419376614</v>
+        <v>14.87936820556466</v>
       </c>
       <c r="C16" t="n">
-        <v>3.719842051391165</v>
+        <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
-        <v>14.87936820556466</v>
+        <v>37.19842051391164</v>
       </c>
     </row>
     <row r="17">
@@ -1607,13 +1607,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>7.555530331883453</v>
+        <v>12.74995743505333</v>
       </c>
       <c r="C17" t="n">
         <v>3.305544520199011</v>
       </c>
       <c r="D17" t="n">
-        <v>6.611089040398022</v>
+        <v>33.52766584773283</v>
       </c>
     </row>
     <row r="18">
@@ -1621,13 +1621,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>2.675262494072558</v>
+        <v>11.23610247510475</v>
       </c>
       <c r="C18" t="n">
-        <v>1.605157496443535</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="D18" t="n">
-        <v>1.070104997629023</v>
+        <v>28.35778243716912</v>
       </c>
     </row>
     <row r="19">
@@ -1635,13 +1635,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>9.628981483252716</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>21.66520833731861</v>
       </c>
     </row>
     <row r="20">
@@ -1649,13 +1649,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>9.41496048372691</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>14.79493790299943</v>
       </c>
     </row>
     <row r="21">
@@ -1663,13 +1663,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>38.87194551912564</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>12.03179266068175</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.776567537080403</v>
       </c>
     </row>
   </sheetData>
@@ -1708,13 +1708,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>101.4832601879928</v>
+        <v>91.25246736203677</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1227184630308513</v>
+        <v>0.2739076094848601</v>
       </c>
       <c r="D2" t="n">
-        <v>26.92835777978576</v>
+        <v>53.93918236672825</v>
       </c>
     </row>
     <row r="3">
@@ -1722,13 +1722,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>322.2194140108456</v>
+        <v>290.6660427963531</v>
       </c>
       <c r="C3" t="n">
-        <v>1.040652566501619</v>
+        <v>1.88986433067511</v>
       </c>
       <c r="D3" t="n">
-        <v>65.83109230826987</v>
+        <v>116.440186462193</v>
       </c>
     </row>
     <row r="4">
@@ -1736,13 +1736,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>535.6003140334814</v>
+        <v>486.0809598312723</v>
       </c>
       <c r="C4" t="n">
-        <v>4.518002934943822</v>
+        <v>6.993970645054278</v>
       </c>
       <c r="D4" t="n">
-        <v>75.08308267309181</v>
+        <v>107.7301208301152</v>
       </c>
     </row>
     <row r="5">
@@ -1750,13 +1750,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>660.0044378725246</v>
+        <v>593.6628367580463</v>
       </c>
       <c r="C5" t="n">
-        <v>10.92194320974577</v>
+        <v>15.46252634188727</v>
       </c>
       <c r="D5" t="n">
-        <v>49.2837347531899</v>
+        <v>69.63045592370504</v>
       </c>
     </row>
     <row r="6">
@@ -1764,13 +1764,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>667.8957259192604</v>
+        <v>627.8050766686376</v>
       </c>
       <c r="C6" t="n">
-        <v>16.1006623496477</v>
+        <v>21.9774041072691</v>
       </c>
       <c r="D6" t="n">
-        <v>35.98498035146259</v>
+        <v>44.23656980565704</v>
       </c>
     </row>
     <row r="7">
@@ -1778,13 +1778,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>587.1882106485385</v>
+        <v>578.5046522044755</v>
       </c>
       <c r="C7" t="n">
-        <v>14.85187926984575</v>
+        <v>20.54110721595601</v>
       </c>
       <c r="D7" t="n">
-        <v>29.22466566001905</v>
+        <v>31.9794497181356</v>
       </c>
     </row>
     <row r="8">
@@ -1792,13 +1792,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>493.6816505575511</v>
+        <v>494.3492389964389</v>
       </c>
       <c r="C8" t="n">
-        <v>9.262789589568655</v>
+        <v>13.4352173326176</v>
       </c>
       <c r="D8" t="n">
-        <v>32.3780392860598</v>
+        <v>30.20837685967435</v>
       </c>
     </row>
     <row r="9">
@@ -1806,13 +1806,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>399.3749660876023</v>
+        <v>433.0999632238888</v>
       </c>
       <c r="C9" t="n">
-        <v>5.546874528994477</v>
+        <v>7.543749359432489</v>
       </c>
       <c r="D9" t="n">
-        <v>36.49843440078366</v>
+        <v>32.72655972106742</v>
       </c>
     </row>
     <row r="10">
@@ -1820,13 +1820,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>217.5160213529233</v>
+        <v>315.3128189114693</v>
       </c>
       <c r="C10" t="n">
-        <v>4.555309347705201</v>
+        <v>4.840016181936776</v>
       </c>
       <c r="D10" t="n">
-        <v>35.87306111317846</v>
+        <v>35.44600086183109</v>
       </c>
     </row>
     <row r="11">
@@ -1834,13 +1834,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>74.27706780790517</v>
+        <v>151.3972769673091</v>
       </c>
       <c r="C11" t="n">
-        <v>4.264712027248144</v>
+        <v>3.553926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>36.25005223160922</v>
+        <v>38.20471191076462</v>
       </c>
     </row>
     <row r="12">
@@ -1848,13 +1848,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>28.20561154301086</v>
+        <v>52.939763203805</v>
       </c>
       <c r="C12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="D12" t="n">
-        <v>35.36549755008285</v>
+        <v>39.70482240285375</v>
       </c>
     </row>
     <row r="13">
@@ -1862,13 +1862,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>20.55288818840698</v>
+        <v>25.23582473766426</v>
       </c>
       <c r="C13" t="n">
-        <v>3.121957699504857</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="D13" t="n">
-        <v>33.30088212805181</v>
+        <v>39.80496066868693</v>
       </c>
     </row>
     <row r="14">
@@ -1876,13 +1876,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14.74977750860408</v>
+        <v>20.28094407433061</v>
       </c>
       <c r="C14" t="n">
-        <v>3.380157345721768</v>
+        <v>3.072870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>28.88498095434966</v>
+        <v>39.02545299151496</v>
       </c>
     </row>
     <row r="15">
@@ -1890,13 +1890,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>12.18348900970292</v>
+        <v>17.5585576904542</v>
       </c>
       <c r="C15" t="n">
-        <v>3.583379120500858</v>
+        <v>3.225041208450772</v>
       </c>
       <c r="D15" t="n">
-        <v>21.14193681095506</v>
+        <v>37.62548076525901</v>
       </c>
     </row>
     <row r="16">
@@ -1904,13 +1904,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>9.919578803709772</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="C16" t="n">
         <v>3.306526267903257</v>
       </c>
       <c r="D16" t="n">
-        <v>12.39947350463721</v>
+        <v>36.78510473042374</v>
       </c>
     </row>
     <row r="17">
@@ -1918,13 +1918,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>5.66664774891259</v>
+        <v>12.27773678931061</v>
       </c>
       <c r="C17" t="n">
         <v>2.833323874456295</v>
       </c>
       <c r="D17" t="n">
-        <v>4.722206457427158</v>
+        <v>32.58322455624739</v>
       </c>
     </row>
     <row r="18">
@@ -1932,13 +1932,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>1.605157496443535</v>
+        <v>10.70104997629023</v>
       </c>
       <c r="C18" t="n">
-        <v>1.070104997629023</v>
+        <v>3.21031499288707</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5350524988145117</v>
+        <v>27.82272993835461</v>
       </c>
     </row>
     <row r="19">
@@ -1946,13 +1946,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>9.027170140549421</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>21.06339699461531</v>
       </c>
     </row>
     <row r="20">
@@ -1960,13 +1960,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>8.742463306317845</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2.68998870963626</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -1974,13 +1974,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>37.30838653485146</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>12.12522562382673</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.79812899011386</v>
       </c>
     </row>
   </sheetData>
@@ -2019,13 +2019,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>101.5824167061217</v>
+        <v>90.00761127305182</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09817477042468103</v>
+        <v>0.2248202242725195</v>
       </c>
       <c r="D2" t="n">
-        <v>29.08133049519902</v>
+        <v>59.39573610693203</v>
       </c>
     </row>
     <row r="3">
@@ -2033,13 +2033,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>324.5805172395592</v>
+        <v>287.6766210369216</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9179341034707678</v>
+        <v>1.703332266868216</v>
       </c>
       <c r="D3" t="n">
-        <v>66.0519855417254</v>
+        <v>116.9801476995287</v>
       </c>
     </row>
     <row r="4">
@@ -2047,13 +2047,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>560.1174994516371</v>
+        <v>489.5013688328681</v>
       </c>
       <c r="C4" t="n">
-        <v>4.135121330287565</v>
+        <v>6.470699118690727</v>
       </c>
       <c r="D4" t="n">
-        <v>76.48698189016474</v>
+        <v>113.8051756239945</v>
       </c>
     </row>
     <row r="5">
@@ -2061,13 +2061,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>713.8042120652498</v>
+        <v>628.3921617957773</v>
       </c>
       <c r="C5" t="n">
-        <v>10.38198197241002</v>
+        <v>14.55440971545897</v>
       </c>
       <c r="D5" t="n">
-        <v>50.97724954301564</v>
+        <v>72.10936887692823</v>
       </c>
     </row>
     <row r="6">
@@ -2075,13 +2075,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>752.8669714695261</v>
+        <v>678.5221630700279</v>
       </c>
       <c r="C6" t="n">
-        <v>16.26166897314417</v>
+        <v>22.13841073076558</v>
       </c>
       <c r="D6" t="n">
-        <v>36.38749691020379</v>
+        <v>45.96739100824416</v>
       </c>
     </row>
     <row r="7">
@@ -2089,13 +2089,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>652.7041619437451</v>
+        <v>631.8636216779938</v>
       </c>
       <c r="C7" t="n">
-        <v>15.69029180927252</v>
+        <v>21.85861263505523</v>
       </c>
       <c r="D7" t="n">
-        <v>28.92523261022377</v>
+        <v>32.63820242768521</v>
       </c>
     </row>
     <row r="8">
@@ -2103,13 +2103,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>540.3293927248382</v>
+        <v>543.6673349192774</v>
       </c>
       <c r="C8" t="n">
-        <v>10.18072369303942</v>
+        <v>14.93729132011522</v>
       </c>
       <c r="D8" t="n">
-        <v>32.04424506661589</v>
+        <v>30.12492830481337</v>
       </c>
     </row>
     <row r="9">
@@ -2117,13 +2117,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>430.1046509782317</v>
+        <v>455.8421487927661</v>
       </c>
       <c r="C9" t="n">
-        <v>5.768749510154256</v>
+        <v>8.653124265231384</v>
       </c>
       <c r="D9" t="n">
-        <v>35.72187196672443</v>
+        <v>32.28280975874785</v>
       </c>
     </row>
     <row r="10">
@@ -2131,13 +2131,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>244.4208171878072</v>
+        <v>347.4846911796373</v>
       </c>
       <c r="C10" t="n">
-        <v>4.697662764820988</v>
+        <v>5.124723016168351</v>
       </c>
       <c r="D10" t="n">
-        <v>35.44600086183109</v>
+        <v>35.3036474447153</v>
       </c>
     </row>
     <row r="11">
@@ -2145,13 +2145,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>88.3150782309303</v>
+        <v>192.6228265640411</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.731623023842126</v>
       </c>
       <c r="D11" t="n">
-        <v>35.18387422479719</v>
+        <v>37.49392657288993</v>
       </c>
     </row>
     <row r="12">
@@ -2159,13 +2159,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>30.15830772675777</v>
+        <v>76.15515116612933</v>
       </c>
       <c r="C12" t="n">
-        <v>3.037527396939631</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>34.49763257952867</v>
+        <v>39.05392367493812</v>
       </c>
     </row>
     <row r="13">
@@ -2173,13 +2173,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19.25207248027995</v>
+        <v>30.95941385342317</v>
       </c>
       <c r="C13" t="n">
-        <v>3.121957699504857</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="D13" t="n">
-        <v>32.00006641992479</v>
+        <v>39.02447124381072</v>
       </c>
     </row>
     <row r="14">
@@ -2187,13 +2187,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13.52062938288707</v>
+        <v>20.58823110575986</v>
       </c>
       <c r="C14" t="n">
-        <v>3.380157345721768</v>
+        <v>3.072870314292517</v>
       </c>
       <c r="D14" t="n">
-        <v>26.42668470291564</v>
+        <v>38.41087892865646</v>
       </c>
     </row>
     <row r="15">
@@ -2201,13 +2201,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>11.10847527355266</v>
+        <v>17.20021977840412</v>
       </c>
       <c r="C15" t="n">
-        <v>3.225041208450772</v>
+        <v>2.866703296400686</v>
       </c>
       <c r="D15" t="n">
-        <v>18.63357142660446</v>
+        <v>37.26714285320892</v>
       </c>
     </row>
     <row r="16">
@@ -2215,13 +2215,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8.266315669758143</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="C16" t="n">
         <v>2.89321048441535</v>
       </c>
       <c r="D16" t="n">
-        <v>9.919578803709772</v>
+        <v>35.95847316344792</v>
       </c>
     </row>
     <row r="17">
@@ -2229,13 +2229,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>3.777765165941727</v>
+        <v>11.8055161435679</v>
       </c>
       <c r="C17" t="n">
-        <v>1.888882582970863</v>
+        <v>2.833323874456295</v>
       </c>
       <c r="D17" t="n">
-        <v>3.305544520199011</v>
+        <v>32.11100391050468</v>
       </c>
     </row>
     <row r="18">
@@ -2243,13 +2243,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.5350524988145117</v>
+        <v>10.16599747747572</v>
       </c>
       <c r="C18" t="n">
-        <v>0.5350524988145117</v>
+        <v>2.675262494072558</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>27.28767743954009</v>
       </c>
     </row>
     <row r="19">
@@ -2257,13 +2257,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>8.425358797846126</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>2.407245370813179</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>20.46158565191202</v>
       </c>
     </row>
     <row r="20">
@@ -2271,13 +2271,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>8.06996612890878</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>2.68998870963626</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>14.12244072559037</v>
       </c>
     </row>
     <row r="21">
@@ -2285,13 +2285,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>35.66949669902862</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>11.26405158916693</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.816012897291734</v>
       </c>
     </row>
   </sheetData>
@@ -2330,13 +2330,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>86.03742355707773</v>
+        <v>77.6582069013312</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09032078879070655</v>
+        <v>0.2051852701875834</v>
       </c>
       <c r="D2" t="n">
-        <v>24.27960247372787</v>
+        <v>49.31318718431729</v>
       </c>
     </row>
     <row r="3">
@@ -2344,13 +2344,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>375.5577667825748</v>
+        <v>325.6064435904971</v>
       </c>
       <c r="C3" t="n">
-        <v>1.413716694115407</v>
+        <v>2.43473430653209</v>
       </c>
       <c r="D3" t="n">
-        <v>65.39421457988004</v>
+        <v>113.4016773175491</v>
       </c>
     </row>
     <row r="4">
@@ -2358,13 +2358,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>505.2122773439299</v>
+        <v>439.548082145382</v>
       </c>
       <c r="C4" t="n">
-        <v>6.815292562881358</v>
+        <v>9.814531799355363</v>
       </c>
       <c r="D4" t="n">
-        <v>67.78280674431252</v>
+        <v>100.3022176997839</v>
       </c>
     </row>
     <row r="5">
@@ -2372,13 +2372,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>424.1640956198345</v>
+        <v>382.2680123411018</v>
       </c>
       <c r="C5" t="n">
-        <v>11.19192382841364</v>
+        <v>15.58524480491812</v>
       </c>
       <c r="D5" t="n">
-        <v>43.14781160164732</v>
+        <v>58.51216317310991</v>
       </c>
     </row>
     <row r="6">
@@ -2386,13 +2386,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>405.3341746523807</v>
+        <v>392.4133931167884</v>
       </c>
       <c r="C6" t="n">
-        <v>10.30442390377452</v>
+        <v>14.36984114706057</v>
       </c>
       <c r="D6" t="n">
-        <v>24.03023855684918</v>
+        <v>29.58496706747763</v>
       </c>
     </row>
     <row r="7">
@@ -2400,13 +2400,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>358.2417007750696</v>
+        <v>360.4575053435547</v>
       </c>
       <c r="C7" t="n">
-        <v>7.126506585127596</v>
+        <v>10.4801567428347</v>
       </c>
       <c r="D7" t="n">
-        <v>22.51736534460484</v>
+        <v>21.13997331554657</v>
       </c>
     </row>
     <row r="8">
@@ -2414,13 +2414,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>298.9127235120263</v>
+        <v>316.7707142522758</v>
       </c>
       <c r="C8" t="n">
-        <v>4.172427743048944</v>
+        <v>6.342090169434394</v>
       </c>
       <c r="D8" t="n">
-        <v>26.28629478120835</v>
+        <v>23.78283813537898</v>
       </c>
     </row>
     <row r="9">
@@ -2428,13 +2428,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>175.9468600597048</v>
+        <v>250.1640412576509</v>
       </c>
       <c r="C9" t="n">
-        <v>3.549999698556465</v>
+        <v>3.882812170296134</v>
       </c>
       <c r="D9" t="n">
-        <v>27.06874770149305</v>
+        <v>26.95781021091316</v>
       </c>
     </row>
     <row r="10">
@@ -2442,13 +2442,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>65.34021845614647</v>
+        <v>142.4957705329033</v>
       </c>
       <c r="C10" t="n">
-        <v>3.131775176547325</v>
+        <v>2.847068342315751</v>
       </c>
       <c r="D10" t="n">
-        <v>27.61656292046278</v>
+        <v>29.32480392585223</v>
       </c>
     </row>
     <row r="11">
@@ -2456,13 +2456,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>22.7451308119901</v>
+        <v>57.57361236784993</v>
       </c>
       <c r="C11" t="n">
-        <v>2.310052348092745</v>
+        <v>2.665445017030089</v>
       </c>
       <c r="D11" t="n">
-        <v>27.54293184264426</v>
+        <v>31.27455486648638</v>
       </c>
     </row>
     <row r="12">
@@ -2470,13 +2470,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.75370449942107</v>
+        <v>23.64932044760141</v>
       </c>
       <c r="C12" t="n">
-        <v>2.386628669023996</v>
+        <v>2.603594911662541</v>
       </c>
       <c r="D12" t="n">
-        <v>26.03594911662541</v>
+        <v>31.89403766786613</v>
       </c>
     </row>
     <row r="13">
@@ -2484,13 +2484,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>10.40652566501619</v>
+        <v>15.86995163914969</v>
       </c>
       <c r="C13" t="n">
-        <v>2.601631416254048</v>
+        <v>2.341468274628643</v>
       </c>
       <c r="D13" t="n">
-        <v>21.853703896534</v>
+        <v>31.73990327829938</v>
       </c>
     </row>
     <row r="14">
@@ -2498,13 +2498,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>8.604036880019047</v>
+        <v>13.52062938288707</v>
       </c>
       <c r="C14" t="n">
-        <v>2.458296251434013</v>
+        <v>2.151009220004762</v>
       </c>
       <c r="D14" t="n">
-        <v>15.36435157146258</v>
+        <v>31.03599017435442</v>
       </c>
     </row>
     <row r="15">
@@ -2512,13 +2512,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>6.450082416901544</v>
+        <v>11.10847527355266</v>
       </c>
       <c r="C15" t="n">
         <v>2.150027472300515</v>
       </c>
       <c r="D15" t="n">
-        <v>8.241771977151972</v>
+        <v>30.45872252425729</v>
       </c>
     </row>
     <row r="16">
@@ -2526,13 +2526,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>2.89321048441535</v>
+        <v>9.506263020221864</v>
       </c>
       <c r="C16" t="n">
-        <v>1.239947350463722</v>
+        <v>2.066578917439536</v>
       </c>
       <c r="D16" t="n">
-        <v>2.479894700927443</v>
+        <v>27.27884171020187</v>
       </c>
     </row>
     <row r="17">
@@ -2540,13 +2540,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>0</v>
+        <v>8.02775097762617</v>
       </c>
       <c r="C17" t="n">
-        <v>0</v>
+        <v>1.888882582970863</v>
       </c>
       <c r="D17" t="n">
-        <v>0</v>
+        <v>23.13881164139307</v>
       </c>
     </row>
     <row r="18">
@@ -2554,13 +2554,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>0</v>
+        <v>6.42062998577414</v>
       </c>
       <c r="C18" t="n">
-        <v>0</v>
+        <v>1.605157496443535</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>17.65673246087889</v>
       </c>
     </row>
     <row r="19">
@@ -2568,13 +2568,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>0</v>
+        <v>6.619924769736241</v>
       </c>
       <c r="C19" t="n">
-        <v>0</v>
+        <v>1.805434028109884</v>
       </c>
       <c r="D19" t="n">
-        <v>0</v>
+        <v>12.03622685406589</v>
       </c>
     </row>
     <row r="20">
@@ -2582,13 +2582,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>23.53740120931727</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>7.397468951499714</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>1.34499435481813</v>
       </c>
     </row>
     <row r="21">
@@ -2641,13 +2641,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>18.25952555128643</v>
+        <v>19.6074651492173</v>
       </c>
       <c r="C2" t="n">
-        <v>1.976258128648829</v>
+        <v>2.961932823712627</v>
       </c>
       <c r="D2" t="n">
-        <v>7.955101647511905</v>
+        <v>11.48448464427919</v>
       </c>
     </row>
     <row r="3">
@@ -2655,13 +2655,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.6381360077604268</v>
+        <v>0.6086835766330224</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4221515128261284</v>
+        <v>0.4123340357836604</v>
       </c>
       <c r="D3" t="n">
-        <v>18.03470532701391</v>
+        <v>17.8039946165159</v>
       </c>
     </row>
     <row r="4">
@@ -2669,13 +2669,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>3.624612524079224</v>
+        <v>3.57356164345839</v>
       </c>
       <c r="C4" t="n">
         <v>1.301797455831271</v>
       </c>
       <c r="D4" t="n">
-        <v>33.11925880276615</v>
+        <v>33.43832680664636</v>
       </c>
     </row>
     <row r="5">
@@ -2683,13 +2683,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.185010536754907</v>
+        <v>6.160466844148737</v>
       </c>
       <c r="C5" t="n">
-        <v>1.423534171157875</v>
+        <v>1.448077863764045</v>
       </c>
       <c r="D5" t="n">
-        <v>16.49336143134642</v>
+        <v>17.20512851692536</v>
       </c>
     </row>
     <row r="6">
@@ -2697,13 +2697,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>8.45284773356504</v>
+        <v>8.372344421816802</v>
       </c>
       <c r="C6" t="n">
-        <v>1.610066234964769</v>
+        <v>1.56981457909065</v>
       </c>
       <c r="D6" t="n">
-        <v>18.8377749490878</v>
+        <v>18.75727163733956</v>
       </c>
     </row>
     <row r="7">
@@ -2711,13 +2711,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>9.761517423326035</v>
+        <v>9.881290643244144</v>
       </c>
       <c r="C7" t="n">
-        <v>2.036144738607885</v>
+        <v>1.976258128648829</v>
       </c>
       <c r="D7" t="n">
-        <v>24.79305652304895</v>
+        <v>24.73316991308989</v>
       </c>
     </row>
     <row r="8">
@@ -2725,13 +2725,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>11.09865779651019</v>
+        <v>11.01520924164921</v>
       </c>
       <c r="C8" t="n">
-        <v>2.420008090968388</v>
+        <v>2.336559536107409</v>
       </c>
       <c r="D8" t="n">
-        <v>30.45872252425729</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -2745,7 +2745,7 @@
         <v>2.662499773917349</v>
       </c>
       <c r="D9" t="n">
-        <v>34.61249706092553</v>
+        <v>34.94530953266521</v>
       </c>
     </row>
     <row r="10">
@@ -2753,13 +2753,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>12.66945412330509</v>
+        <v>12.5271007061893</v>
       </c>
       <c r="C10" t="n">
         <v>2.989421759431538</v>
       </c>
       <c r="D10" t="n">
-        <v>38.29306920414684</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -2767,13 +2767,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>12.43874341280708</v>
+        <v>12.61643974727576</v>
       </c>
       <c r="C11" t="n">
-        <v>3.020837685967435</v>
+        <v>3.198534020436107</v>
       </c>
       <c r="D11" t="n">
-        <v>41.5809422656694</v>
+        <v>41.40324593120072</v>
       </c>
     </row>
     <row r="12">
@@ -2781,13 +2781,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>11.71617710248143</v>
+        <v>11.93314334511998</v>
       </c>
       <c r="C12" t="n">
         <v>3.254493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>42.09145107187774</v>
+        <v>42.74234979979338</v>
       </c>
     </row>
     <row r="13">
@@ -2795,13 +2795,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.18701508989241</v>
+        <v>11.44717823151781</v>
       </c>
       <c r="C13" t="n">
         <v>3.121957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>42.40659208494097</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -2823,13 +2823,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.541826921753</v>
       </c>
       <c r="C15" t="n">
         <v>3.941717032550943</v>
       </c>
       <c r="D15" t="n">
-        <v>41.56719779780995</v>
+        <v>42.64221153396021</v>
       </c>
     </row>
     <row r="16">
@@ -2837,13 +2837,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="C16" t="n">
-        <v>4.546473618366978</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>39.67831521483909</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -2851,13 +2851,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="C17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.722206457427158</v>
       </c>
       <c r="D17" t="n">
-        <v>33.52766584773283</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -2865,13 +2865,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14.98146996680633</v>
+        <v>14.44641746799181</v>
       </c>
       <c r="C18" t="n">
-        <v>5.885577486959628</v>
+        <v>5.350524988145117</v>
       </c>
       <c r="D18" t="n">
-        <v>28.35778243716912</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -2882,10 +2882,10 @@
         <v>15.04528356758237</v>
       </c>
       <c r="C19" t="n">
-        <v>6.619924769736241</v>
+        <v>6.018113427032947</v>
       </c>
       <c r="D19" t="n">
-        <v>21.06339699461531</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -2896,10 +2896,10 @@
         <v>15.46743508040849</v>
       </c>
       <c r="C20" t="n">
-        <v>9.41496048372691</v>
+        <v>6.724971774090649</v>
       </c>
       <c r="D20" t="n">
-        <v>9.41496048372691</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="21">
@@ -2907,10 +2907,10 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>7.140292944694478</v>
+        <v>19.76455576296041</v>
       </c>
       <c r="C21" t="n">
-        <v>1.428058588938895</v>
+        <v>8.361927438175554</v>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2952,13 +2952,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>11.98517597344506</v>
+        <v>12.9737959116216</v>
       </c>
       <c r="C2" t="n">
-        <v>1.063232763699296</v>
+        <v>1.607120991852028</v>
       </c>
       <c r="D2" t="n">
-        <v>17.27581435163112</v>
+        <v>27.89636101617311</v>
       </c>
     </row>
     <row r="3">
@@ -2966,13 +2966,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>73.04693793448392</v>
+        <v>77.64642592888023</v>
       </c>
       <c r="C3" t="n">
-        <v>3.858268477689965</v>
+        <v>5.659775514982861</v>
       </c>
       <c r="D3" t="n">
-        <v>19.19807635654638</v>
+        <v>21.12721059539136</v>
       </c>
     </row>
     <row r="4">
@@ -2980,10 +2980,10 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.595340019401067</v>
+        <v>1.454950097693773</v>
       </c>
       <c r="C4" t="n">
-        <v>1.186932974434394</v>
+        <v>1.161407534123977</v>
       </c>
       <c r="D4" t="n">
         <v>34.14027641518283</v>
@@ -2994,13 +2994,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>6.185010536754907</v>
+        <v>6.062292073724056</v>
       </c>
       <c r="C5" t="n">
         <v>1.84077694546277</v>
       </c>
       <c r="D5" t="n">
-        <v>21.13211933391259</v>
+        <v>22.38384765682728</v>
       </c>
     </row>
     <row r="6">
@@ -3008,13 +3008,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.620145753914496</v>
+        <v>9.418887474543901</v>
       </c>
       <c r="C6" t="n">
         <v>1.851576170209485</v>
       </c>
       <c r="D6" t="n">
-        <v>19.48180144307371</v>
+        <v>19.68305972244431</v>
       </c>
     </row>
     <row r="7">
@@ -3022,13 +3022,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>11.67788894201581</v>
+        <v>11.5581157220977</v>
       </c>
       <c r="C7" t="n">
-        <v>2.155917958525996</v>
+        <v>2.09603134856694</v>
       </c>
       <c r="D7" t="n">
-        <v>24.97271635292611</v>
+        <v>24.55351008321272</v>
       </c>
     </row>
     <row r="8">
@@ -3036,13 +3036,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>12.60073178400781</v>
+        <v>12.68418033886879</v>
       </c>
       <c r="C8" t="n">
-        <v>2.586905200690345</v>
+        <v>2.420008090968388</v>
       </c>
       <c r="D8" t="n">
-        <v>30.62561963397925</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="9">
@@ -3050,13 +3050,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>13.64531134132641</v>
+        <v>13.31249886958674</v>
       </c>
       <c r="C9" t="n">
         <v>2.773437264497239</v>
       </c>
       <c r="D9" t="n">
-        <v>35.27812200440487</v>
+        <v>34.61249706092553</v>
       </c>
     </row>
     <row r="10">
@@ -3070,7 +3070,7 @@
         <v>3.131775176547325</v>
       </c>
       <c r="D10" t="n">
-        <v>38.72012945549421</v>
+        <v>38.29306920414684</v>
       </c>
     </row>
     <row r="11">
@@ -3084,7 +3084,7 @@
         <v>3.198534020436107</v>
       </c>
       <c r="D11" t="n">
-        <v>41.40324593120072</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -3092,13 +3092,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>13.23494080095125</v>
+        <v>13.66887328622834</v>
       </c>
       <c r="C12" t="n">
         <v>3.254493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>41.65751858660066</v>
+        <v>42.95931604243193</v>
       </c>
     </row>
     <row r="13">
@@ -3106,13 +3106,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>11.96750451476862</v>
+        <v>12.74799393964483</v>
       </c>
       <c r="C13" t="n">
         <v>3.121957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>41.62610266006477</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -3126,7 +3126,7 @@
         <v>3.380157345721768</v>
       </c>
       <c r="D14" t="n">
-        <v>41.48374924294897</v>
+        <v>42.40561033723673</v>
       </c>
     </row>
     <row r="15">
@@ -3134,13 +3134,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.541826921753</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>40.49218406165969</v>
+        <v>42.28387362191012</v>
       </c>
     </row>
     <row r="16">
@@ -3148,13 +3148,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="C16" t="n">
-        <v>4.546473618366978</v>
+        <v>4.133157834879071</v>
       </c>
       <c r="D16" t="n">
-        <v>37.61173629739955</v>
+        <v>41.33157834879071</v>
       </c>
     </row>
     <row r="17">
@@ -3162,13 +3162,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15.11106066376691</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="C17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="D17" t="n">
-        <v>31.63878326476196</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -3176,13 +3176,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>14.44641746799181</v>
+        <v>13.9113649691773</v>
       </c>
       <c r="C18" t="n">
-        <v>5.885577486959628</v>
+        <v>4.815472489330605</v>
       </c>
       <c r="D18" t="n">
-        <v>25.68251994309656</v>
+        <v>30.49799243242716</v>
       </c>
     </row>
     <row r="19">
@@ -3193,10 +3193,10 @@
         <v>14.44347222487907</v>
       </c>
       <c r="C19" t="n">
-        <v>7.221736112439537</v>
+        <v>5.416302084329653</v>
       </c>
       <c r="D19" t="n">
-        <v>16.24890625298896</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -3204,13 +3204,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>16.13993225781756</v>
+        <v>14.79493790299943</v>
       </c>
       <c r="C20" t="n">
-        <v>7.397468951499714</v>
+        <v>6.052474596681584</v>
       </c>
       <c r="D20" t="n">
-        <v>5.37997741927252</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="21">
@@ -3218,13 +3218,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>24.97040182250987</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>9.363900683441203</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>0.7803250569534336</v>
       </c>
     </row>
   </sheetData>
@@ -3263,13 +3263,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.904991456866312</v>
+        <v>5.353470231257857</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8384125394267761</v>
+        <v>1.276272015520853</v>
       </c>
       <c r="D2" t="n">
-        <v>17.25421590213769</v>
+        <v>28.65034325303467</v>
       </c>
     </row>
     <row r="3">
@@ -3277,13 +3277,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>48.84685702480005</v>
+        <v>52.46459731494955</v>
       </c>
       <c r="C3" t="n">
-        <v>3.98589567924205</v>
+        <v>5.880668748438395</v>
       </c>
       <c r="D3" t="n">
-        <v>25.20146356801562</v>
+        <v>32.14732857556181</v>
       </c>
     </row>
     <row r="4">
@@ -3291,13 +3291,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>157.0707969501514</v>
+        <v>165.2006496890193</v>
       </c>
       <c r="C4" t="n">
-        <v>4.900884539600077</v>
+        <v>6.981207924899069</v>
       </c>
       <c r="D4" t="n">
-        <v>34.91880234465055</v>
+        <v>35.36549755008285</v>
       </c>
     </row>
     <row r="5">
@@ -3305,13 +3305,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>3.166136346195964</v>
+        <v>2.82252464970958</v>
       </c>
       <c r="C5" t="n">
         <v>1.963495408493621</v>
       </c>
       <c r="D5" t="n">
-        <v>25.37817815478006</v>
+        <v>27.09623663721197</v>
       </c>
     </row>
     <row r="6">
@@ -3319,13 +3319,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>9.821404033285093</v>
+        <v>9.378635818669782</v>
       </c>
       <c r="C6" t="n">
-        <v>2.294344384824796</v>
+        <v>2.254092728950677</v>
       </c>
       <c r="D6" t="n">
-        <v>20.7296027751714</v>
+        <v>21.17237098978672</v>
       </c>
     </row>
     <row r="7">
@@ -3333,13 +3333,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.35471402086936</v>
+        <v>13.05528097107408</v>
       </c>
       <c r="C7" t="n">
         <v>2.335577788403162</v>
       </c>
       <c r="D7" t="n">
-        <v>25.21226279276233</v>
+        <v>24.852943133008</v>
       </c>
     </row>
     <row r="8">
@@ -3347,13 +3347,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>14.77039421039326</v>
+        <v>14.6034971006713</v>
       </c>
       <c r="C8" t="n">
-        <v>2.670353755551324</v>
+        <v>2.586905200690345</v>
       </c>
       <c r="D8" t="n">
-        <v>30.79251674370121</v>
+        <v>29.54078842078653</v>
       </c>
     </row>
     <row r="9">
@@ -3364,10 +3364,10 @@
         <v>15.30937370002476</v>
       </c>
       <c r="C9" t="n">
-        <v>2.995312245657018</v>
+        <v>2.884374755077128</v>
       </c>
       <c r="D9" t="n">
-        <v>36.27655941962388</v>
+        <v>34.72343455150543</v>
       </c>
     </row>
     <row r="10">
@@ -3375,13 +3375,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>15.80122929985241</v>
+        <v>15.37416904850505</v>
       </c>
       <c r="C10" t="n">
         <v>3.274128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>38.72012945549421</v>
+        <v>38.00836236991527</v>
       </c>
     </row>
     <row r="11">
@@ -3395,7 +3395,7 @@
         <v>3.37623035490478</v>
       </c>
       <c r="D11" t="n">
-        <v>41.04785326226338</v>
+        <v>41.22554959673205</v>
       </c>
     </row>
     <row r="12">
@@ -3403,13 +3403,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>14.75370449942107</v>
+        <v>15.18763698469816</v>
       </c>
       <c r="C12" t="n">
         <v>3.254493639578176</v>
       </c>
       <c r="D12" t="n">
-        <v>41.22358610132357</v>
+        <v>42.52538355715483</v>
       </c>
     </row>
     <row r="13">
@@ -3417,13 +3417,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>13.26832022289564</v>
+        <v>14.30897278939726</v>
       </c>
       <c r="C13" t="n">
         <v>3.121957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>41.36593951843936</v>
+        <v>42.92691836819179</v>
       </c>
     </row>
     <row r="14">
@@ -3431,13 +3431,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12.29148125717007</v>
+        <v>13.21334235145782</v>
       </c>
       <c r="C14" t="n">
         <v>3.380157345721768</v>
       </c>
       <c r="D14" t="n">
-        <v>40.56188814866123</v>
+        <v>42.09832330580748</v>
       </c>
     </row>
     <row r="15">
@@ -3445,13 +3445,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.25850274585317</v>
+        <v>12.541826921753</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>39.41717032550944</v>
+        <v>42.28387362191012</v>
       </c>
     </row>
     <row r="16">
@@ -3459,13 +3459,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13.63942085510094</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="C16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
-        <v>35.54515737996002</v>
+        <v>40.91826256530281</v>
       </c>
     </row>
     <row r="17">
@@ -3473,13 +3473,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15.58328130950962</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="C17" t="n">
-        <v>5.194427103169874</v>
+        <v>4.249985811684442</v>
       </c>
       <c r="D17" t="n">
-        <v>29.7499006817911</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -3490,10 +3490,10 @@
         <v>13.9113649691773</v>
       </c>
       <c r="C18" t="n">
-        <v>5.885577486959628</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="D18" t="n">
-        <v>21.93715245139498</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -3501,13 +3501,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>14.44347222487907</v>
+        <v>13.84166088217578</v>
       </c>
       <c r="C19" t="n">
-        <v>7.221736112439537</v>
+        <v>4.814490741626358</v>
       </c>
       <c r="D19" t="n">
-        <v>12.03622685406589</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -3515,13 +3515,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>10.08745766113597</v>
+        <v>14.12244072559037</v>
       </c>
       <c r="C20" t="n">
-        <v>4.707480241863455</v>
+        <v>5.37997741927252</v>
       </c>
       <c r="D20" t="n">
-        <v>2.68998870963626</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="21">
@@ -3529,13 +3529,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>29.6686443038019</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>10.42411826890337</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>1.603710502908211</v>
       </c>
     </row>
   </sheetData>
@@ -3574,13 +3574,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>21.74276640595411</v>
+        <v>24.53583862453629</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6960591223109885</v>
+        <v>1.112320148911636</v>
       </c>
       <c r="D2" t="n">
-        <v>26.80858455986765</v>
+        <v>46.79893131374121</v>
       </c>
     </row>
     <row r="3">
@@ -3588,13 +3588,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>13.95063487734718</v>
+        <v>23.27232932917064</v>
       </c>
       <c r="C3" t="n">
-        <v>3.652101459798134</v>
+        <v>5.409429850399925</v>
       </c>
       <c r="D3" t="n">
-        <v>30.26237298340793</v>
+        <v>41.74391238457438</v>
       </c>
     </row>
     <row r="4">
@@ -3602,13 +3602,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>116.6895503790716</v>
+        <v>122.3944862884499</v>
       </c>
       <c r="C4" t="n">
-        <v>7.096072406295946</v>
+        <v>10.26122700478766</v>
       </c>
       <c r="D4" t="n">
-        <v>37.71383805864122</v>
+        <v>40.30467025014855</v>
       </c>
     </row>
     <row r="5">
@@ -3616,13 +3616,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>226.9555255292564</v>
+        <v>241.2644983186537</v>
       </c>
       <c r="C5" t="n">
-        <v>4.786020058203201</v>
+        <v>6.405903770210439</v>
       </c>
       <c r="D5" t="n">
-        <v>28.59340188618836</v>
+        <v>30.704159450319</v>
       </c>
     </row>
     <row r="6">
@@ -3630,13 +3630,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>5.957245069369646</v>
+        <v>5.2327152636355</v>
       </c>
       <c r="C6" t="n">
-        <v>2.61635763181775</v>
+        <v>2.576105975943631</v>
       </c>
       <c r="D6" t="n">
-        <v>22.46042397775853</v>
+        <v>23.54721868635975</v>
       </c>
     </row>
     <row r="7">
@@ -3644,13 +3644,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>13.95358012045992</v>
+        <v>13.05528097107408</v>
       </c>
       <c r="C7" t="n">
-        <v>2.694897448157494</v>
+        <v>2.635010838198439</v>
       </c>
       <c r="D7" t="n">
-        <v>25.57158245251667</v>
+        <v>25.03260296288517</v>
       </c>
     </row>
     <row r="8">
@@ -3658,13 +3658,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>16.94005663677871</v>
+        <v>16.43936530761284</v>
       </c>
       <c r="C8" t="n">
-        <v>2.837250865273282</v>
+        <v>2.753802310412303</v>
       </c>
       <c r="D8" t="n">
-        <v>31.29320807286708</v>
+        <v>29.45733986592554</v>
       </c>
     </row>
     <row r="9">
@@ -3672,13 +3672,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>17.74999849278232</v>
+        <v>17.52812351162255</v>
       </c>
       <c r="C9" t="n">
-        <v>3.106249736236907</v>
+        <v>2.995312245657018</v>
       </c>
       <c r="D9" t="n">
-        <v>36.94218436310322</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -3686,13 +3686,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>17.65182372235765</v>
+        <v>17.36711688812608</v>
       </c>
       <c r="C10" t="n">
-        <v>3.4164820107789</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>38.72012945549421</v>
+        <v>37.86600895279948</v>
       </c>
     </row>
     <row r="11">
@@ -3700,13 +3700,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>17.41424077792992</v>
+        <v>17.05884810899257</v>
       </c>
       <c r="C11" t="n">
         <v>3.553926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>40.69246059332603</v>
+        <v>41.40324593120072</v>
       </c>
     </row>
     <row r="12">
@@ -3714,13 +3714,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>16.27246819789088</v>
+        <v>16.92336692580652</v>
       </c>
       <c r="C12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.471459882216721</v>
       </c>
       <c r="D12" t="n">
-        <v>40.78965361604648</v>
+        <v>42.30841731451629</v>
       </c>
     </row>
     <row r="13">
@@ -3728,13 +3728,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>14.56913593102267</v>
+        <v>15.60978849752428</v>
       </c>
       <c r="C13" t="n">
         <v>3.121957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>41.10577637681396</v>
+        <v>43.1870815098172</v>
       </c>
     </row>
     <row r="14">
@@ -3742,13 +3742,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>12.90605532002857</v>
+        <v>14.44249047717483</v>
       </c>
       <c r="C14" t="n">
         <v>3.380157345721768</v>
       </c>
       <c r="D14" t="n">
-        <v>39.64002705437346</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -3759,10 +3759,10 @@
         <v>13.25850274585317</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>37.9838186773091</v>
+        <v>42.28387362191012</v>
       </c>
     </row>
     <row r="16">
@@ -3770,13 +3770,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>13.63942085510094</v>
+        <v>12.81278928812512</v>
       </c>
       <c r="C16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
-        <v>33.47857846252048</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -3784,13 +3784,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16.05550195525234</v>
+        <v>13.69439872653876</v>
       </c>
       <c r="C17" t="n">
-        <v>5.194427103169874</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="D17" t="n">
-        <v>27.38879745307752</v>
+        <v>35.8887690764464</v>
       </c>
     </row>
     <row r="18">
@@ -3801,10 +3801,10 @@
         <v>13.37631247036279</v>
       </c>
       <c r="C18" t="n">
-        <v>5.885577486959628</v>
+        <v>4.280419990516093</v>
       </c>
       <c r="D18" t="n">
-        <v>18.1917849596934</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -3812,13 +3812,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>12.63803819676919</v>
+        <v>13.84166088217578</v>
       </c>
       <c r="C19" t="n">
-        <v>6.619924769736241</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="D19" t="n">
-        <v>8.425358797846126</v>
+        <v>24.67426505083508</v>
       </c>
     </row>
     <row r="20">
@@ -3826,13 +3826,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>6.052474596681584</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>2.68998870963626</v>
+        <v>4.707480241863455</v>
       </c>
       <c r="D20" t="n">
-        <v>1.34499435481813</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="21">
@@ -3840,13 +3840,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>32.91293740621457</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>10.69670465701974</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.468470305466093</v>
       </c>
     </row>
   </sheetData>
@@ -3885,13 +3885,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>27.36523550817559</v>
+        <v>32.1807079975062</v>
       </c>
       <c r="C2" t="n">
-        <v>0.5085453107998478</v>
+        <v>0.8423395302437634</v>
       </c>
       <c r="D2" t="n">
-        <v>25.34970747135689</v>
+        <v>45.10148953309847</v>
       </c>
     </row>
     <row r="3">
@@ -3899,13 +3899,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>79.58046890624645</v>
+        <v>87.95968556199298</v>
       </c>
       <c r="C3" t="n">
-        <v>3.23485868549324</v>
+        <v>4.89401230567035</v>
       </c>
       <c r="D3" t="n">
-        <v>38.7201294554942</v>
+        <v>57.72676500971245</v>
       </c>
     </row>
     <row r="4">
@@ -3913,13 +3913,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>43.40601124786423</v>
+        <v>61.52907386826035</v>
       </c>
       <c r="C4" t="n">
-        <v>7.951174656694918</v>
+        <v>11.39710909860122</v>
       </c>
       <c r="D4" t="n">
-        <v>40.89175537728815</v>
+        <v>46.54564040604553</v>
       </c>
     </row>
     <row r="5">
@@ -3927,13 +3927,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>204.6207652576415</v>
+        <v>210.8057757943964</v>
       </c>
       <c r="C5" t="n">
-        <v>7.952156404399165</v>
+        <v>11.24101121362598</v>
       </c>
       <c r="D5" t="n">
-        <v>32.20132469929538</v>
+        <v>35.14656781203582</v>
       </c>
     </row>
     <row r="6">
@@ -3941,13 +3941,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>273.107485105899</v>
+        <v>297.1779753186223</v>
       </c>
       <c r="C6" t="n">
-        <v>4.347178834404877</v>
+        <v>5.313218575383739</v>
       </c>
       <c r="D6" t="n">
-        <v>24.2717484920939</v>
+        <v>25.84156307118455</v>
       </c>
     </row>
     <row r="7">
@@ -3955,13 +3955,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>10.18072369303942</v>
+        <v>8.743445054022093</v>
       </c>
       <c r="C7" t="n">
         <v>3.054217107911827</v>
       </c>
       <c r="D7" t="n">
-        <v>25.99078872223005</v>
+        <v>25.81112889235289</v>
       </c>
     </row>
     <row r="8">
@@ -3969,13 +3969,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>18.10833640483241</v>
+        <v>16.77315952705676</v>
       </c>
       <c r="C8" t="n">
-        <v>3.087596529856218</v>
+        <v>3.00414797499524</v>
       </c>
       <c r="D8" t="n">
-        <v>31.37665662772806</v>
+        <v>29.37389131106456</v>
       </c>
     </row>
     <row r="9">
@@ -3983,13 +3983,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.07968579496001</v>
+        <v>19.41406085148067</v>
       </c>
       <c r="C9" t="n">
-        <v>3.328124717396686</v>
+        <v>3.106249736236907</v>
       </c>
       <c r="D9" t="n">
-        <v>37.82968428774233</v>
+        <v>34.83437204208531</v>
       </c>
     </row>
     <row r="10">
@@ -3997,13 +3997,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>20.07183181332604</v>
+        <v>19.64477156197868</v>
       </c>
       <c r="C10" t="n">
-        <v>3.558835427894688</v>
+        <v>3.274128593663113</v>
       </c>
       <c r="D10" t="n">
-        <v>38.72012945549421</v>
+        <v>37.5813021185679</v>
       </c>
     </row>
     <row r="11">
@@ -4011,13 +4011,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>19.19120412261664</v>
+        <v>18.8358114536793</v>
       </c>
       <c r="C11" t="n">
-        <v>3.731623023842126</v>
+        <v>3.553926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>40.33706792438868</v>
+        <v>41.04785326226338</v>
       </c>
     </row>
     <row r="12">
@@ -4025,13 +4025,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>18.00819813899924</v>
+        <v>18.22516438163779</v>
       </c>
       <c r="C12" t="n">
-        <v>3.254493639578176</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="D12" t="n">
-        <v>40.35572113076938</v>
+        <v>42.52538355715483</v>
       </c>
     </row>
     <row r="13">
@@ -4039,13 +4039,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>15.86995163914969</v>
+        <v>17.43093048890212</v>
       </c>
       <c r="C13" t="n">
         <v>3.121957699504857</v>
       </c>
       <c r="D13" t="n">
-        <v>40.32528695193774</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -4053,13 +4053,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>13.82791641431633</v>
+        <v>15.67163860289184</v>
       </c>
       <c r="C14" t="n">
         <v>3.380157345721768</v>
       </c>
       <c r="D14" t="n">
-        <v>39.02545299151496</v>
+        <v>41.79103627437823</v>
       </c>
     </row>
     <row r="15">
@@ -4067,13 +4067,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.25850274585317</v>
+        <v>14.33351648200343</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>36.55046702910875</v>
+        <v>41.56719779780995</v>
       </c>
     </row>
     <row r="16">
@@ -4081,13 +4081,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14.05273663858884</v>
+        <v>13.22610507161303</v>
       </c>
       <c r="C16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
-        <v>31.41199954508094</v>
+        <v>40.5049467818149</v>
       </c>
     </row>
     <row r="17">
@@ -4095,13 +4095,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>16.05550195525234</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="C17" t="n">
-        <v>5.194427103169874</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="D17" t="n">
-        <v>24.0832529328785</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -4109,13 +4109,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>12.84125997154828</v>
+        <v>13.37631247036279</v>
       </c>
       <c r="C18" t="n">
-        <v>5.885577486959628</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="D18" t="n">
-        <v>14.44641746799181</v>
+        <v>29.96293993361265</v>
       </c>
     </row>
     <row r="19">
@@ -4123,13 +4123,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>10.23079282595601</v>
+        <v>13.23984953947248</v>
       </c>
       <c r="C19" t="n">
-        <v>5.416302084329653</v>
+        <v>4.212679398923063</v>
       </c>
       <c r="D19" t="n">
-        <v>5.416302084329653</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -4137,13 +4137,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>3.362485887045325</v>
+        <v>13.4499435481813</v>
       </c>
       <c r="C20" t="n">
-        <v>1.34499435481813</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="D20" t="n">
-        <v>0.672497177409065</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="21">
@@ -4151,13 +4151,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>36.24137067619694</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>10.95669346024559</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.528467721595135</v>
       </c>
     </row>
   </sheetData>
@@ -4196,13 +4196,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>40.20649547972387</v>
+        <v>43.27936579401639</v>
       </c>
       <c r="C2" t="n">
-        <v>0.377972866135022</v>
+        <v>0.6567892141411161</v>
       </c>
       <c r="D2" t="n">
-        <v>28.63365354206247</v>
+        <v>52.39783847106076</v>
       </c>
     </row>
     <row r="3">
@@ -4210,13 +4210,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>103.8885420633975</v>
+        <v>118.5018566411113</v>
       </c>
       <c r="C3" t="n">
-        <v>2.714532402242431</v>
+        <v>4.201880174176348</v>
       </c>
       <c r="D3" t="n">
-        <v>44.23264281484004</v>
+        <v>69.1641257641878</v>
       </c>
     </row>
     <row r="4">
@@ -4224,13 +4224,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>155.8455758152514</v>
+        <v>169.3485337394621</v>
       </c>
       <c r="C4" t="n">
-        <v>7.951174656694918</v>
+        <v>11.5119735799981</v>
       </c>
       <c r="D4" t="n">
-        <v>46.34143688356219</v>
+        <v>55.60717171624359</v>
       </c>
     </row>
     <row r="5">
@@ -4238,13 +4238,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>105.3415286656828</v>
+        <v>127.3081335482052</v>
       </c>
       <c r="C5" t="n">
-        <v>10.38198197241002</v>
+        <v>14.57895340806514</v>
       </c>
       <c r="D5" t="n">
-        <v>35.22019888985433</v>
+        <v>39.80986940720817</v>
       </c>
     </row>
     <row r="6">
@@ -4252,13 +4252,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>307.6836575017674</v>
+        <v>316.4585184823254</v>
       </c>
       <c r="C6" t="n">
-        <v>7.084291433844984</v>
+        <v>9.660397409788615</v>
       </c>
       <c r="D6" t="n">
-        <v>26.40508625342222</v>
+        <v>28.29691407950582</v>
       </c>
     </row>
     <row r="7">
@@ -4266,10 +4266,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>262.4231248405809</v>
+        <v>296.6183791272015</v>
       </c>
       <c r="C7" t="n">
-        <v>4.07228947721577</v>
+        <v>4.551382356888213</v>
       </c>
       <c r="D7" t="n">
         <v>26.52976821186155</v>
@@ -4280,13 +4280,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>15.35453409442011</v>
+        <v>13.01797455831271</v>
       </c>
       <c r="C8" t="n">
-        <v>3.421390749300134</v>
+        <v>3.337942194439155</v>
       </c>
       <c r="D8" t="n">
-        <v>32.12769362147687</v>
+        <v>29.70768553050848</v>
       </c>
     </row>
     <row r="9">
@@ -4294,13 +4294,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>21.74374815365835</v>
+        <v>20.1906232855399</v>
       </c>
       <c r="C9" t="n">
-        <v>3.549999698556465</v>
+        <v>3.328124717396686</v>
       </c>
       <c r="D9" t="n">
-        <v>37.94062177832222</v>
+        <v>34.50155957034565</v>
       </c>
     </row>
     <row r="10">
@@ -4308,13 +4308,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>22.49183990429443</v>
+        <v>21.6377194015997</v>
       </c>
       <c r="C10" t="n">
-        <v>3.701188845010476</v>
+        <v>3.4164820107789</v>
       </c>
       <c r="D10" t="n">
-        <v>38.57777603837842</v>
+        <v>37.72365553568369</v>
       </c>
     </row>
     <row r="11">
@@ -4322,13 +4322,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>21.14586380177204</v>
+        <v>20.96816746730337</v>
       </c>
       <c r="C11" t="n">
-        <v>3.909319358310797</v>
+        <v>3.553926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>39.98167525545134</v>
+        <v>40.51476425885736</v>
       </c>
     </row>
     <row r="12">
@@ -4339,10 +4339,10 @@
         <v>19.7439280801076</v>
       </c>
       <c r="C12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="D12" t="n">
-        <v>39.92178864549229</v>
+        <v>42.09145107187774</v>
       </c>
     </row>
     <row r="13">
@@ -4350,13 +4350,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>17.43093048890212</v>
+        <v>18.73174619702914</v>
       </c>
       <c r="C13" t="n">
-        <v>3.121957699504857</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="D13" t="n">
-        <v>39.80496066868693</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -4364,13 +4364,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>14.74977750860408</v>
+        <v>17.20807376003809</v>
       </c>
       <c r="C14" t="n">
         <v>3.380157345721768</v>
       </c>
       <c r="D14" t="n">
-        <v>37.79630486579796</v>
+        <v>41.48374924294897</v>
       </c>
     </row>
     <row r="15">
@@ -4378,13 +4378,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.61684065790326</v>
+        <v>15.0501923061036</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>35.1171153809084</v>
+        <v>41.56719779780995</v>
       </c>
     </row>
     <row r="16">
@@ -4392,13 +4392,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14.87936820556466</v>
+        <v>13.63942085510094</v>
       </c>
       <c r="C16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
-        <v>28.9321048441535</v>
+        <v>40.09163099832699</v>
       </c>
     </row>
     <row r="17">
@@ -4406,13 +4406,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>15.11106066376691</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="C17" t="n">
-        <v>5.194427103169874</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="D17" t="n">
-        <v>20.77770841267949</v>
+        <v>35.41654843070368</v>
       </c>
     </row>
     <row r="18">
@@ -4420,13 +4420,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>11.77115497391926</v>
+        <v>12.84125997154828</v>
       </c>
       <c r="C18" t="n">
-        <v>5.350524988145117</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="D18" t="n">
-        <v>11.23610247510475</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -4434,13 +4434,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>7.823547455142832</v>
+        <v>12.63803819676919</v>
       </c>
       <c r="C19" t="n">
-        <v>4.212679398923063</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="D19" t="n">
-        <v>3.610868056219768</v>
+        <v>24.07245370813179</v>
       </c>
     </row>
     <row r="20">
@@ -4448,13 +4448,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>2.017491532227195</v>
+        <v>12.77744637077223</v>
       </c>
       <c r="C20" t="n">
-        <v>0.672497177409065</v>
+        <v>4.03498306445439</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="21">
@@ -4462,13 +4462,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>38.76748335098809</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>11.19949519028545</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.584498890065873</v>
       </c>
     </row>
   </sheetData>
@@ -4507,13 +4507,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>53.19403585920492</v>
+        <v>56.22469102221483</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2896155727528091</v>
+        <v>0.5213080309550563</v>
       </c>
       <c r="D2" t="n">
-        <v>35.95552792033518</v>
+        <v>68.15783436733481</v>
       </c>
     </row>
     <row r="3">
@@ -4521,13 +4521,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>145.7993515576938</v>
+        <v>153.6336982375834</v>
       </c>
       <c r="C3" t="n">
-        <v>2.233476027161494</v>
+        <v>3.553926689373454</v>
       </c>
       <c r="D3" t="n">
-        <v>50.81526117181491</v>
+        <v>80.71438750465153</v>
       </c>
     </row>
     <row r="4">
@@ -4535,13 +4535,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>213.0480875508961</v>
+        <v>234.9106271767683</v>
       </c>
       <c r="C4" t="n">
-        <v>7.478954010952201</v>
+        <v>10.96317661332413</v>
       </c>
       <c r="D4" t="n">
-        <v>51.95703375185395</v>
+        <v>65.30683903420207</v>
       </c>
     </row>
     <row r="5">
@@ -4549,13 +4549,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>217.5307475684871</v>
+        <v>231.8642640504905</v>
       </c>
       <c r="C5" t="n">
-        <v>11.8055161435679</v>
+        <v>16.66516727958961</v>
       </c>
       <c r="D5" t="n">
-        <v>38.28816046562561</v>
+        <v>44.64497685062371</v>
       </c>
     </row>
     <row r="6">
@@ -4563,13 +4563,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>213.7362926915731</v>
+        <v>233.4998557257657</v>
       </c>
       <c r="C6" t="n">
-        <v>9.94215900090745</v>
+        <v>13.72581465307466</v>
       </c>
       <c r="D6" t="n">
-        <v>28.45792070300229</v>
+        <v>31.47679489356124</v>
       </c>
     </row>
     <row r="7">
@@ -4577,13 +4577,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>368.3026512481908</v>
+        <v>386.9273869454572</v>
       </c>
       <c r="C7" t="n">
-        <v>5.809001166028376</v>
+        <v>7.366053024963818</v>
       </c>
       <c r="D7" t="n">
-        <v>27.12863431145211</v>
+        <v>27.36818075128833</v>
       </c>
     </row>
     <row r="8">
@@ -4591,13 +4591,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>202.7799883121787</v>
+        <v>241.5835663225338</v>
       </c>
       <c r="C8" t="n">
-        <v>3.922082078466008</v>
+        <v>4.088979188187965</v>
       </c>
       <c r="D8" t="n">
-        <v>32.46148784092078</v>
+        <v>30.0414797499524</v>
       </c>
     </row>
     <row r="9">
@@ -4605,13 +4605,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>20.63437324785945</v>
+        <v>17.52812351162255</v>
       </c>
       <c r="C9" t="n">
-        <v>3.771874679716245</v>
+        <v>3.549999698556465</v>
       </c>
       <c r="D9" t="n">
-        <v>38.38437174064178</v>
+        <v>34.16874709860598</v>
       </c>
     </row>
     <row r="10">
@@ -4619,13 +4619,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>24.20008090968388</v>
+        <v>22.776546738526</v>
       </c>
       <c r="C10" t="n">
-        <v>3.843542262126263</v>
+        <v>3.558835427894688</v>
       </c>
       <c r="D10" t="n">
-        <v>38.43542262126263</v>
+        <v>37.43894870145212</v>
       </c>
     </row>
     <row r="11">
@@ -4633,13 +4633,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>23.10052348092744</v>
+        <v>22.7451308119901</v>
       </c>
       <c r="C11" t="n">
-        <v>3.909319358310797</v>
+        <v>3.553926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>39.626282586514</v>
+        <v>40.51476425885736</v>
       </c>
     </row>
     <row r="12">
@@ -4647,13 +4647,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>21.26269177857742</v>
+        <v>21.47965802121596</v>
       </c>
       <c r="C12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="D12" t="n">
-        <v>39.27088991757666</v>
+        <v>41.65751858660066</v>
       </c>
     </row>
     <row r="13">
@@ -4661,13 +4661,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>18.73174619702914</v>
+        <v>20.03256190515617</v>
       </c>
       <c r="C13" t="n">
-        <v>3.121957699504857</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="D13" t="n">
-        <v>38.76430810218531</v>
+        <v>42.66675522656638</v>
       </c>
     </row>
     <row r="14">
@@ -4675,13 +4675,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15.36435157146258</v>
+        <v>18.12993485432585</v>
       </c>
       <c r="C14" t="n">
         <v>3.380157345721768</v>
       </c>
       <c r="D14" t="n">
-        <v>36.8744437715102</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -4689,13 +4689,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>13.97517856995334</v>
+        <v>16.12520604225386</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>33.32542582065798</v>
+        <v>40.85052197370977</v>
       </c>
     </row>
     <row r="16">
@@ -4703,13 +4703,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>15.29268398905256</v>
+        <v>14.05273663858884</v>
       </c>
       <c r="C16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
-        <v>26.45221014322606</v>
+        <v>40.09163099832699</v>
       </c>
     </row>
     <row r="17">
@@ -4717,13 +4717,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>14.16661937228147</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="C17" t="n">
-        <v>5.194427103169874</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="D17" t="n">
-        <v>17.47216389248049</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -4731,13 +4731,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>10.16599747747572</v>
+        <v>12.84125997154828</v>
       </c>
       <c r="C18" t="n">
-        <v>4.815472489330605</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="D18" t="n">
-        <v>8.560839981032187</v>
+        <v>29.42788743479814</v>
       </c>
     </row>
     <row r="19">
@@ -4745,13 +4745,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
-        <v>5.416302084329653</v>
+        <v>12.03622685406589</v>
       </c>
       <c r="C19" t="n">
-        <v>3.009056713516474</v>
+        <v>3.610868056219768</v>
       </c>
       <c r="D19" t="n">
-        <v>1.805434028109884</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -4759,13 +4759,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.672497177409065</v>
+        <v>12.10494919336317</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>16.81242943522663</v>
       </c>
     </row>
     <row r="21">
@@ -4773,13 +4773,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>40.40694687307139</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>11.41935455108539</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.635235665635091</v>
       </c>
     </row>
   </sheetData>
@@ -4818,13 +4818,13 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>71.53504646994384</v>
+        <v>73.78423046037328</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2012582793705961</v>
+        <v>0.3769911184307752</v>
       </c>
       <c r="D2" t="n">
-        <v>37.01974243173873</v>
+        <v>71.20027050279568</v>
       </c>
     </row>
     <row r="3">
@@ -4832,13 +4832,13 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>187.4499979103647</v>
+        <v>191.9954897810275</v>
       </c>
       <c r="C3" t="n">
-        <v>1.826050729899067</v>
+        <v>3.009056713516474</v>
       </c>
       <c r="D3" t="n">
-        <v>57.33406592801373</v>
+        <v>95.04790398665494</v>
       </c>
     </row>
     <row r="4">
@@ -4846,13 +4846,13 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>286.3826775627243</v>
+        <v>297.2565151349619</v>
       </c>
       <c r="C4" t="n">
-        <v>6.879106163657401</v>
+        <v>10.13359980323558</v>
       </c>
       <c r="D4" t="n">
-        <v>57.80235958293945</v>
+        <v>75.17242171417827</v>
       </c>
     </row>
     <row r="5">
@@ -4860,13 +4860,13 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>305.2744486355458</v>
+        <v>324.3203540979338</v>
       </c>
       <c r="C5" t="n">
-        <v>12.27184630308513</v>
+        <v>17.37693436516855</v>
       </c>
       <c r="D5" t="n">
-        <v>41.25794727097221</v>
+        <v>50.2654824574367</v>
       </c>
     </row>
     <row r="6">
@@ -4874,13 +4874,13 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>287.960346123449</v>
+        <v>301.4043991854048</v>
       </c>
       <c r="C6" t="n">
-        <v>12.39751000922872</v>
+        <v>17.14720540237479</v>
       </c>
       <c r="D6" t="n">
-        <v>30.39000018496002</v>
+        <v>33.97239755775664</v>
       </c>
     </row>
     <row r="7">
@@ -4888,13 +4888,13 @@
         <v>5</v>
       </c>
       <c r="B7" t="n">
-        <v>331.2927262934947</v>
+        <v>347.0429047127262</v>
       </c>
       <c r="C7" t="n">
-        <v>7.964919124554372</v>
+        <v>10.71970318267092</v>
       </c>
       <c r="D7" t="n">
-        <v>27.66761380108361</v>
+        <v>28.32636651063322</v>
       </c>
     </row>
     <row r="8">
@@ -4902,13 +4902,13 @@
         <v>6</v>
       </c>
       <c r="B8" t="n">
-        <v>342.9735604786231</v>
+        <v>378.8564390688441</v>
       </c>
       <c r="C8" t="n">
-        <v>4.756567627075796</v>
+        <v>5.591053175685585</v>
       </c>
       <c r="D8" t="n">
-        <v>33.04562772494764</v>
+        <v>30.29182541453534</v>
       </c>
     </row>
     <row r="9">
@@ -4916,13 +4916,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>125.9140518081746</v>
+        <v>165.2968609640354</v>
       </c>
       <c r="C9" t="n">
-        <v>3.993749660876023</v>
+        <v>3.882812170296134</v>
       </c>
       <c r="D9" t="n">
-        <v>38.2734342500619</v>
+        <v>33.83593462686631</v>
       </c>
     </row>
     <row r="10">
@@ -4930,13 +4930,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>24.48478774391545</v>
+        <v>21.21065915025234</v>
       </c>
       <c r="C10" t="n">
-        <v>3.98589567924205</v>
+        <v>3.701188845010476</v>
       </c>
       <c r="D10" t="n">
-        <v>37.86600895279948</v>
+        <v>37.01188845010476</v>
       </c>
     </row>
     <row r="11">
@@ -4944,13 +4944,13 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>24.6997904911455</v>
+        <v>23.81130881880213</v>
       </c>
       <c r="C11" t="n">
-        <v>4.08701569277947</v>
+        <v>3.553926689373453</v>
       </c>
       <c r="D11" t="n">
-        <v>39.09319358310798</v>
+        <v>40.51476425885736</v>
       </c>
     </row>
     <row r="12">
@@ -4958,13 +4958,13 @@
         <v>10</v>
       </c>
       <c r="B12" t="n">
-        <v>22.56448923440869</v>
+        <v>22.99842171968578</v>
       </c>
       <c r="C12" t="n">
-        <v>3.471459882216721</v>
+        <v>3.688426124855267</v>
       </c>
       <c r="D12" t="n">
-        <v>38.61999118966103</v>
+        <v>41.22358610132357</v>
       </c>
     </row>
     <row r="13">
@@ -4972,13 +4972,13 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>19.77239876353076</v>
+        <v>21.07321447165778</v>
       </c>
       <c r="C13" t="n">
-        <v>3.121957699504857</v>
+        <v>3.382120841130262</v>
       </c>
       <c r="D13" t="n">
-        <v>38.24398181893451</v>
+        <v>42.14642894331557</v>
       </c>
     </row>
     <row r="14">
@@ -4986,13 +4986,13 @@
         <v>12</v>
       </c>
       <c r="B14" t="n">
-        <v>15.97892563432109</v>
+        <v>19.0517959486136</v>
       </c>
       <c r="C14" t="n">
         <v>3.380157345721768</v>
       </c>
       <c r="D14" t="n">
-        <v>35.33800861436394</v>
+        <v>41.17646221151972</v>
       </c>
     </row>
     <row r="15">
@@ -5000,13 +5000,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="n">
-        <v>14.69185439405351</v>
+        <v>16.84188186635403</v>
       </c>
       <c r="C15" t="n">
-        <v>3.941717032550943</v>
+        <v>3.583379120500858</v>
       </c>
       <c r="D15" t="n">
-        <v>31.17539834835746</v>
+        <v>40.1338461496096</v>
       </c>
     </row>
     <row r="16">
@@ -5014,13 +5014,13 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>14.87936820556466</v>
+        <v>14.46605242207675</v>
       </c>
       <c r="C16" t="n">
-        <v>4.546473618366978</v>
+        <v>3.719842051391165</v>
       </c>
       <c r="D16" t="n">
-        <v>23.55899965881071</v>
+        <v>39.26499943135118</v>
       </c>
     </row>
     <row r="17">
@@ -5028,13 +5028,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="n">
-        <v>12.74995743505333</v>
+        <v>13.22217808079604</v>
       </c>
       <c r="C17" t="n">
-        <v>4.722206457427158</v>
+        <v>3.777765165941727</v>
       </c>
       <c r="D17" t="n">
-        <v>14.63884001802419</v>
+        <v>34.94432778496098</v>
       </c>
     </row>
     <row r="18">
@@ -5042,13 +5042,13 @@
         <v>16</v>
       </c>
       <c r="B18" t="n">
-        <v>8.560839981032187</v>
+        <v>12.30620747273377</v>
       </c>
       <c r="C18" t="n">
-        <v>4.280419990516093</v>
+        <v>3.745367491701582</v>
       </c>
       <c r="D18" t="n">
-        <v>5.885577486959628</v>
+        <v>28.89283493598363</v>
       </c>
     </row>
     <row r="19">
@@ -5056,13 +5056,13 @@
         <v>17</v>
       </c>
       <c r="B19" t="n">
+        <v>11.4344155113626</v>
+      </c>
+      <c r="C19" t="n">
         <v>3.610868056219768</v>
       </c>
-      <c r="C19" t="n">
-        <v>1.805434028109884</v>
-      </c>
       <c r="D19" t="n">
-        <v>0.6018113427032947</v>
+        <v>23.47064236542849</v>
       </c>
     </row>
     <row r="20">
@@ -5070,13 +5070,13 @@
         <v>18</v>
       </c>
       <c r="B20" t="n">
-        <v>0</v>
+        <v>11.43245201595411</v>
       </c>
       <c r="C20" t="n">
-        <v>0</v>
+        <v>3.362485887045325</v>
       </c>
       <c r="D20" t="n">
-        <v>0</v>
+        <v>16.13993225781756</v>
       </c>
     </row>
     <row r="21">
@@ -5084,13 +5084,13 @@
         <v>19</v>
       </c>
       <c r="B21" t="n">
-        <v>0</v>
+        <v>41.09098882286887</v>
       </c>
       <c r="C21" t="n">
-        <v>0</v>
+        <v>11.61267075428903</v>
       </c>
       <c r="D21" t="n">
-        <v>0</v>
+        <v>2.679847097143622</v>
       </c>
     </row>
   </sheetData>
